--- a/Gmail_Compose_Test_Cases.xlsx
+++ b/Gmail_Compose_Test_Cases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Interviews\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Interviews\Test_artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="228">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -1706,6 +1706,9 @@
 3. Enter the string "Incubyte" in the "Subject" field. 
 4. Enter the string " QA test for Incubyte" in the email body text area. 
 5. Click the "Send" button.</t>
+  </si>
+  <si>
+    <t>Scenario Type</t>
   </si>
 </sst>
 </file>
@@ -2269,10 +2272,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -3096,9 +3099,8 @@
       <c r="A1" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="5">
-        <f>H1</f>
-        <v>0</v>
+      <c r="B1" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -3112,16 +3114,16 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>103</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -3129,182 +3131,182 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="8"/>
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="7" t="s">
         <v>105</v>
       </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
       <c r="E6" s="8"/>
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
       <c r="E7" s="7" t="s">
         <v>106</v>
       </c>
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="8"/>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
       <c r="E9" s="7" t="s">
         <v>107</v>
       </c>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="8"/>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="7" t="s">
         <v>108</v>
       </c>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="8"/>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
       <c r="E13" s="7" t="s">
         <v>109</v>
       </c>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="8"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="7" t="s">
         <v>110</v>
       </c>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
       <c r="E16" s="8"/>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
       <c r="E17" s="7" t="s">
         <v>111</v>
       </c>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
       <c r="E18" s="8"/>
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
       <c r="E19" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
       <c r="E21" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>115</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -3312,96 +3314,96 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
       <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
       <c r="E24" s="7" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
       <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
       <c r="E26" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
       <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
       <c r="E28" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
       <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
       <c r="E30" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
       <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="13" t="s">
         <v>123</v>
       </c>
       <c r="E33" s="7" t="s">
@@ -3409,112 +3411,112 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
       <c r="E34" s="8"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
       <c r="E35" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
       <c r="E36" s="8"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
       <c r="E37" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
       <c r="E38" s="8"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
       <c r="E39" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
       <c r="E40" s="8"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
       <c r="E41" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
       <c r="E42" s="8"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
       <c r="E43" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
       <c r="E44" s="8"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="13"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
       <c r="E45" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>131</v>
       </c>
       <c r="E46" s="7" t="s">
@@ -3522,112 +3524,112 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="13"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
       <c r="E48" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="13"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="13"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
       <c r="E50" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
       <c r="E52" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
+      <c r="A53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
       <c r="E53" s="8"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="13"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
+      <c r="A54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
       <c r="E54" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
       <c r="E56" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="13"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
+      <c r="A58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
       <c r="E58" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>140</v>
       </c>
       <c r="E59" s="7" t="s">
@@ -3635,96 +3637,96 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="13"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
       <c r="E60" s="8"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
       <c r="E61" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
+      <c r="A62" s="12"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
+      <c r="A63" s="12"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
       <c r="E63" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="13"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
+      <c r="A64" s="12"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
       <c r="E64" s="8"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
       <c r="E65" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
       <c r="E66" s="8"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
       <c r="E67" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
+      <c r="A68" s="12"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
       <c r="E68" s="8"/>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
       <c r="E69" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="13" t="s">
         <v>148</v>
       </c>
       <c r="E70" s="7" t="s">
@@ -3732,80 +3734,80 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
+      <c r="A71" s="12"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
+      <c r="A72" s="12"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
       <c r="E72" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
+      <c r="A73" s="12"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
+      <c r="A74" s="12"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
       <c r="E74" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
+      <c r="A75" s="12"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
+      <c r="A76" s="12"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
       <c r="E76" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
+      <c r="A77" s="12"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
+      <c r="A78" s="12"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
       <c r="E78" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E79" s="7" t="s">
@@ -3813,96 +3815,96 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
+      <c r="A80" s="12"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
+      <c r="A81" s="12"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
       <c r="E81" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
+      <c r="A82" s="12"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
       <c r="E82" s="8"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
+      <c r="A83" s="12"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
       <c r="E83" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
+      <c r="A84" s="12"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
       <c r="E84" s="8"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
-      <c r="B85" s="12"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
+      <c r="A85" s="12"/>
+      <c r="B85" s="13"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
       <c r="E85" s="7" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
+      <c r="A86" s="12"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
       <c r="E86" s="8"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
+      <c r="A87" s="12"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
       <c r="E87" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
+      <c r="A88" s="12"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
       <c r="E88" s="8"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="12"/>
+      <c r="A89" s="12"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
       <c r="E89" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="13" t="s">
         <v>162</v>
       </c>
       <c r="E90" s="7" t="s">
@@ -3910,80 +3912,80 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="13"/>
-      <c r="B91" s="12"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="12"/>
+      <c r="A91" s="12"/>
+      <c r="B91" s="13"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
       <c r="E91" s="8"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="13"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="12"/>
+      <c r="A92" s="12"/>
+      <c r="B92" s="13"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
       <c r="E92" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
-      <c r="B93" s="12"/>
-      <c r="C93" s="12"/>
-      <c r="D93" s="12"/>
+      <c r="A93" s="12"/>
+      <c r="B93" s="13"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
       <c r="E93" s="8"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="13"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="12"/>
+      <c r="A94" s="12"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
       <c r="E94" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="13"/>
-      <c r="B95" s="12"/>
-      <c r="C95" s="12"/>
-      <c r="D95" s="12"/>
+      <c r="A95" s="12"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="13"/>
       <c r="E95" s="8"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="13"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="12"/>
-      <c r="D96" s="12"/>
+      <c r="A96" s="12"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="13"/>
       <c r="E96" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="13"/>
-      <c r="B97" s="12"/>
-      <c r="C97" s="12"/>
-      <c r="D97" s="12"/>
+      <c r="A97" s="12"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="13"/>
       <c r="E97" s="8"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="13"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="12"/>
-      <c r="D98" s="12"/>
+      <c r="A98" s="12"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="13"/>
       <c r="E98" s="7" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="13" t="s">
         <v>169</v>
       </c>
       <c r="E99" s="7" t="s">
@@ -3991,112 +3993,112 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="13"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="12"/>
+      <c r="A100" s="12"/>
+      <c r="B100" s="13"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
       <c r="E100" s="8"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="13"/>
-      <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="12"/>
+      <c r="A101" s="12"/>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
       <c r="E101" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="13"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12"/>
+      <c r="A102" s="12"/>
+      <c r="B102" s="13"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="13"/>
       <c r="E102" s="8"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="13"/>
-      <c r="B103" s="12"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="12"/>
+      <c r="A103" s="12"/>
+      <c r="B103" s="13"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="13"/>
       <c r="E103" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="13"/>
-      <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="12"/>
+      <c r="A104" s="12"/>
+      <c r="B104" s="13"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="13"/>
       <c r="E104" s="8"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="13"/>
-      <c r="B105" s="12"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="12"/>
+      <c r="A105" s="12"/>
+      <c r="B105" s="13"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="13"/>
       <c r="E105" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="13"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="12"/>
+      <c r="A106" s="12"/>
+      <c r="B106" s="13"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="13"/>
       <c r="E106" s="8"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="13"/>
-      <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="12"/>
+      <c r="A107" s="12"/>
+      <c r="B107" s="13"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="13"/>
       <c r="E107" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="13"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="12"/>
+      <c r="A108" s="12"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="13"/>
       <c r="E108" s="8"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="13"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="12"/>
+      <c r="A109" s="12"/>
+      <c r="B109" s="13"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="13"/>
       <c r="E109" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="13"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="12"/>
+      <c r="A110" s="12"/>
+      <c r="B110" s="13"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="13"/>
       <c r="E110" s="8"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="13"/>
-      <c r="B111" s="12"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="12"/>
+      <c r="A111" s="12"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13"/>
       <c r="E111" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C112" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D112" s="12" t="s">
+      <c r="D112" s="13" t="s">
         <v>178</v>
       </c>
       <c r="E112" s="7" t="s">
@@ -4104,96 +4106,96 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="13"/>
-      <c r="B113" s="12"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="12"/>
+      <c r="A113" s="12"/>
+      <c r="B113" s="13"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
       <c r="E113" s="8"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="13"/>
-      <c r="B114" s="12"/>
-      <c r="C114" s="12"/>
-      <c r="D114" s="12"/>
+      <c r="A114" s="12"/>
+      <c r="B114" s="13"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="13"/>
       <c r="E114" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="13"/>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="12"/>
+      <c r="A115" s="12"/>
+      <c r="B115" s="13"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="13"/>
       <c r="E115" s="8"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="13"/>
-      <c r="B116" s="12"/>
-      <c r="C116" s="12"/>
-      <c r="D116" s="12"/>
+      <c r="A116" s="12"/>
+      <c r="B116" s="13"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="13"/>
       <c r="E116" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="13"/>
-      <c r="B117" s="12"/>
-      <c r="C117" s="12"/>
-      <c r="D117" s="12"/>
+      <c r="A117" s="12"/>
+      <c r="B117" s="13"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="13"/>
       <c r="E117" s="8"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="13"/>
-      <c r="B118" s="12"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="12"/>
+      <c r="A118" s="12"/>
+      <c r="B118" s="13"/>
+      <c r="C118" s="13"/>
+      <c r="D118" s="13"/>
       <c r="E118" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="13"/>
-      <c r="B119" s="12"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12"/>
+      <c r="A119" s="12"/>
+      <c r="B119" s="13"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
       <c r="E119" s="8"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="13"/>
-      <c r="B120" s="12"/>
-      <c r="C120" s="12"/>
-      <c r="D120" s="12"/>
+      <c r="A120" s="12"/>
+      <c r="B120" s="13"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
       <c r="E120" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="13"/>
-      <c r="B121" s="12"/>
-      <c r="C121" s="12"/>
-      <c r="D121" s="12"/>
+      <c r="A121" s="12"/>
+      <c r="B121" s="13"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13"/>
       <c r="E121" s="8"/>
     </row>
     <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="13"/>
-      <c r="B122" s="12"/>
-      <c r="C122" s="12"/>
-      <c r="D122" s="12"/>
+      <c r="A122" s="12"/>
+      <c r="B122" s="13"/>
+      <c r="C122" s="13"/>
+      <c r="D122" s="13"/>
       <c r="E122" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="13" t="s">
         <v>185</v>
       </c>
       <c r="E123" s="7" t="s">
@@ -4201,96 +4203,96 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="13"/>
-      <c r="B124" s="12"/>
-      <c r="C124" s="12"/>
-      <c r="D124" s="12"/>
+      <c r="A124" s="12"/>
+      <c r="B124" s="13"/>
+      <c r="C124" s="13"/>
+      <c r="D124" s="13"/>
       <c r="E124" s="8"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="13"/>
-      <c r="B125" s="12"/>
-      <c r="C125" s="12"/>
-      <c r="D125" s="12"/>
+      <c r="A125" s="12"/>
+      <c r="B125" s="13"/>
+      <c r="C125" s="13"/>
+      <c r="D125" s="13"/>
       <c r="E125" s="7" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="13"/>
-      <c r="B126" s="12"/>
-      <c r="C126" s="12"/>
-      <c r="D126" s="12"/>
+      <c r="A126" s="12"/>
+      <c r="B126" s="13"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="13"/>
       <c r="E126" s="8"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="13"/>
-      <c r="B127" s="12"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="12"/>
+      <c r="A127" s="12"/>
+      <c r="B127" s="13"/>
+      <c r="C127" s="13"/>
+      <c r="D127" s="13"/>
       <c r="E127" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="13"/>
-      <c r="B128" s="12"/>
-      <c r="C128" s="12"/>
-      <c r="D128" s="12"/>
+      <c r="A128" s="12"/>
+      <c r="B128" s="13"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="13"/>
       <c r="E128" s="8"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="13"/>
-      <c r="B129" s="12"/>
-      <c r="C129" s="12"/>
-      <c r="D129" s="12"/>
+      <c r="A129" s="12"/>
+      <c r="B129" s="13"/>
+      <c r="C129" s="13"/>
+      <c r="D129" s="13"/>
       <c r="E129" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="13"/>
-      <c r="B130" s="12"/>
-      <c r="C130" s="12"/>
-      <c r="D130" s="12"/>
+      <c r="A130" s="12"/>
+      <c r="B130" s="13"/>
+      <c r="C130" s="13"/>
+      <c r="D130" s="13"/>
       <c r="E130" s="8"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="13"/>
-      <c r="B131" s="12"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="12"/>
+      <c r="A131" s="12"/>
+      <c r="B131" s="13"/>
+      <c r="C131" s="13"/>
+      <c r="D131" s="13"/>
       <c r="E131" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="13"/>
-      <c r="B132" s="12"/>
-      <c r="C132" s="12"/>
-      <c r="D132" s="12"/>
+      <c r="A132" s="12"/>
+      <c r="B132" s="13"/>
+      <c r="C132" s="13"/>
+      <c r="D132" s="13"/>
       <c r="E132" s="8"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="13"/>
-      <c r="B133" s="12"/>
-      <c r="C133" s="12"/>
-      <c r="D133" s="12"/>
+      <c r="A133" s="12"/>
+      <c r="B133" s="13"/>
+      <c r="C133" s="13"/>
+      <c r="D133" s="13"/>
       <c r="E133" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="13" t="s">
+      <c r="A134" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D134" s="12" t="s">
+      <c r="D134" s="13" t="s">
         <v>193</v>
       </c>
       <c r="E134" s="7" t="s">
@@ -4298,96 +4300,96 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="13"/>
-      <c r="B135" s="12"/>
-      <c r="C135" s="12"/>
-      <c r="D135" s="12"/>
+      <c r="A135" s="12"/>
+      <c r="B135" s="13"/>
+      <c r="C135" s="13"/>
+      <c r="D135" s="13"/>
       <c r="E135" s="8"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="13"/>
-      <c r="B136" s="12"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12"/>
+      <c r="A136" s="12"/>
+      <c r="B136" s="13"/>
+      <c r="C136" s="13"/>
+      <c r="D136" s="13"/>
       <c r="E136" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="13"/>
-      <c r="B137" s="12"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12"/>
+      <c r="A137" s="12"/>
+      <c r="B137" s="13"/>
+      <c r="C137" s="13"/>
+      <c r="D137" s="13"/>
       <c r="E137" s="8"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="13"/>
-      <c r="B138" s="12"/>
-      <c r="C138" s="12"/>
-      <c r="D138" s="12"/>
+      <c r="A138" s="12"/>
+      <c r="B138" s="13"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
       <c r="E138" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="13"/>
-      <c r="B139" s="12"/>
-      <c r="C139" s="12"/>
-      <c r="D139" s="12"/>
+      <c r="A139" s="12"/>
+      <c r="B139" s="13"/>
+      <c r="C139" s="13"/>
+      <c r="D139" s="13"/>
       <c r="E139" s="8"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="13"/>
-      <c r="B140" s="12"/>
-      <c r="C140" s="12"/>
-      <c r="D140" s="12"/>
+      <c r="A140" s="12"/>
+      <c r="B140" s="13"/>
+      <c r="C140" s="13"/>
+      <c r="D140" s="13"/>
       <c r="E140" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="13"/>
-      <c r="B141" s="12"/>
-      <c r="C141" s="12"/>
-      <c r="D141" s="12"/>
+      <c r="A141" s="12"/>
+      <c r="B141" s="13"/>
+      <c r="C141" s="13"/>
+      <c r="D141" s="13"/>
       <c r="E141" s="8"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="13"/>
-      <c r="B142" s="12"/>
-      <c r="C142" s="12"/>
-      <c r="D142" s="12"/>
+      <c r="A142" s="12"/>
+      <c r="B142" s="13"/>
+      <c r="C142" s="13"/>
+      <c r="D142" s="13"/>
       <c r="E142" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="13"/>
-      <c r="B143" s="12"/>
-      <c r="C143" s="12"/>
-      <c r="D143" s="12"/>
+      <c r="A143" s="12"/>
+      <c r="B143" s="13"/>
+      <c r="C143" s="13"/>
+      <c r="D143" s="13"/>
       <c r="E143" s="8"/>
     </row>
     <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="13"/>
-      <c r="B144" s="12"/>
-      <c r="C144" s="12"/>
-      <c r="D144" s="12"/>
+      <c r="A144" s="12"/>
+      <c r="B144" s="13"/>
+      <c r="C144" s="13"/>
+      <c r="D144" s="13"/>
       <c r="E144" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="13" t="s">
+      <c r="A145" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B145" s="12" t="s">
+      <c r="B145" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C145" s="12" t="s">
+      <c r="C145" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="13" t="s">
         <v>201</v>
       </c>
       <c r="E145" s="7" t="s">
@@ -4395,96 +4397,96 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="13"/>
-      <c r="B146" s="12"/>
-      <c r="C146" s="12"/>
-      <c r="D146" s="12"/>
+      <c r="A146" s="12"/>
+      <c r="B146" s="13"/>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
       <c r="E146" s="8"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="13"/>
-      <c r="B147" s="12"/>
-      <c r="C147" s="12"/>
-      <c r="D147" s="12"/>
+      <c r="A147" s="12"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
       <c r="E147" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="13"/>
-      <c r="B148" s="12"/>
-      <c r="C148" s="12"/>
-      <c r="D148" s="12"/>
+      <c r="A148" s="12"/>
+      <c r="B148" s="13"/>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
       <c r="E148" s="8"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="13"/>
-      <c r="B149" s="12"/>
-      <c r="C149" s="12"/>
-      <c r="D149" s="12"/>
+      <c r="A149" s="12"/>
+      <c r="B149" s="13"/>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
       <c r="E149" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="13"/>
-      <c r="B150" s="12"/>
-      <c r="C150" s="12"/>
-      <c r="D150" s="12"/>
+      <c r="A150" s="12"/>
+      <c r="B150" s="13"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
       <c r="E150" s="8"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="13"/>
-      <c r="B151" s="12"/>
-      <c r="C151" s="12"/>
-      <c r="D151" s="12"/>
+      <c r="A151" s="12"/>
+      <c r="B151" s="13"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
       <c r="E151" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="13"/>
-      <c r="B152" s="12"/>
-      <c r="C152" s="12"/>
-      <c r="D152" s="12"/>
+      <c r="A152" s="12"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
       <c r="E152" s="8"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="13"/>
-      <c r="B153" s="12"/>
-      <c r="C153" s="12"/>
-      <c r="D153" s="12"/>
+      <c r="A153" s="12"/>
+      <c r="B153" s="13"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
       <c r="E153" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="13"/>
-      <c r="B154" s="12"/>
-      <c r="C154" s="12"/>
-      <c r="D154" s="12"/>
+      <c r="A154" s="12"/>
+      <c r="B154" s="13"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
       <c r="E154" s="8"/>
     </row>
     <row r="155" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="13"/>
-      <c r="B155" s="12"/>
-      <c r="C155" s="12"/>
-      <c r="D155" s="12"/>
+      <c r="A155" s="12"/>
+      <c r="B155" s="13"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
       <c r="E155" s="7" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="13" t="s">
+      <c r="A156" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B156" s="12" t="s">
+      <c r="B156" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D156" s="12" t="s">
+      <c r="D156" s="13" t="s">
         <v>209</v>
       </c>
       <c r="E156" s="7" t="s">
@@ -4492,96 +4494,96 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="13"/>
-      <c r="B157" s="12"/>
-      <c r="C157" s="12"/>
-      <c r="D157" s="12"/>
+      <c r="A157" s="12"/>
+      <c r="B157" s="13"/>
+      <c r="C157" s="13"/>
+      <c r="D157" s="13"/>
       <c r="E157" s="8"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="13"/>
-      <c r="B158" s="12"/>
-      <c r="C158" s="12"/>
-      <c r="D158" s="12"/>
+      <c r="A158" s="12"/>
+      <c r="B158" s="13"/>
+      <c r="C158" s="13"/>
+      <c r="D158" s="13"/>
       <c r="E158" s="7" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="13"/>
-      <c r="B159" s="12"/>
-      <c r="C159" s="12"/>
-      <c r="D159" s="12"/>
+      <c r="A159" s="12"/>
+      <c r="B159" s="13"/>
+      <c r="C159" s="13"/>
+      <c r="D159" s="13"/>
       <c r="E159" s="8"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="13"/>
-      <c r="B160" s="12"/>
-      <c r="C160" s="12"/>
-      <c r="D160" s="12"/>
+      <c r="A160" s="12"/>
+      <c r="B160" s="13"/>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
       <c r="E160" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="13"/>
-      <c r="B161" s="12"/>
-      <c r="C161" s="12"/>
-      <c r="D161" s="12"/>
+      <c r="A161" s="12"/>
+      <c r="B161" s="13"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
       <c r="E161" s="8"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="13"/>
-      <c r="B162" s="12"/>
-      <c r="C162" s="12"/>
-      <c r="D162" s="12"/>
+      <c r="A162" s="12"/>
+      <c r="B162" s="13"/>
+      <c r="C162" s="13"/>
+      <c r="D162" s="13"/>
       <c r="E162" s="7" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="13"/>
-      <c r="B163" s="12"/>
-      <c r="C163" s="12"/>
-      <c r="D163" s="12"/>
+      <c r="A163" s="12"/>
+      <c r="B163" s="13"/>
+      <c r="C163" s="13"/>
+      <c r="D163" s="13"/>
       <c r="E163" s="8"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="13"/>
-      <c r="B164" s="12"/>
-      <c r="C164" s="12"/>
-      <c r="D164" s="12"/>
+      <c r="A164" s="12"/>
+      <c r="B164" s="13"/>
+      <c r="C164" s="13"/>
+      <c r="D164" s="13"/>
       <c r="E164" s="7" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="13"/>
-      <c r="B165" s="12"/>
-      <c r="C165" s="12"/>
-      <c r="D165" s="12"/>
+      <c r="A165" s="12"/>
+      <c r="B165" s="13"/>
+      <c r="C165" s="13"/>
+      <c r="D165" s="13"/>
       <c r="E165" s="8"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="13"/>
-      <c r="B166" s="12"/>
-      <c r="C166" s="12"/>
-      <c r="D166" s="12"/>
+      <c r="A166" s="12"/>
+      <c r="B166" s="13"/>
+      <c r="C166" s="13"/>
+      <c r="D166" s="13"/>
       <c r="E166" s="7" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="13" t="s">
+      <c r="A167" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B167" s="12" t="s">
+      <c r="B167" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C167" s="12" t="s">
+      <c r="C167" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D167" s="12" t="s">
+      <c r="D167" s="13" t="s">
         <v>217</v>
       </c>
       <c r="E167" s="7" t="s">
@@ -4589,119 +4591,71 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="13"/>
-      <c r="B168" s="12"/>
-      <c r="C168" s="12"/>
-      <c r="D168" s="12"/>
+      <c r="A168" s="12"/>
+      <c r="B168" s="13"/>
+      <c r="C168" s="13"/>
+      <c r="D168" s="13"/>
       <c r="E168" s="8"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="13"/>
-      <c r="B169" s="12"/>
-      <c r="C169" s="12"/>
-      <c r="D169" s="12"/>
+      <c r="A169" s="12"/>
+      <c r="B169" s="13"/>
+      <c r="C169" s="13"/>
+      <c r="D169" s="13"/>
       <c r="E169" s="7" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="13"/>
-      <c r="B170" s="12"/>
-      <c r="C170" s="12"/>
-      <c r="D170" s="12"/>
+      <c r="A170" s="12"/>
+      <c r="B170" s="13"/>
+      <c r="C170" s="13"/>
+      <c r="D170" s="13"/>
       <c r="E170" s="8"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="13"/>
-      <c r="B171" s="12"/>
-      <c r="C171" s="12"/>
-      <c r="D171" s="12"/>
+      <c r="A171" s="12"/>
+      <c r="B171" s="13"/>
+      <c r="C171" s="13"/>
+      <c r="D171" s="13"/>
       <c r="E171" s="7" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="13"/>
-      <c r="B172" s="12"/>
-      <c r="C172" s="12"/>
-      <c r="D172" s="12"/>
+      <c r="A172" s="12"/>
+      <c r="B172" s="13"/>
+      <c r="C172" s="13"/>
+      <c r="D172" s="13"/>
       <c r="E172" s="8"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="13"/>
-      <c r="B173" s="12"/>
-      <c r="C173" s="12"/>
-      <c r="D173" s="12"/>
+      <c r="A173" s="12"/>
+      <c r="B173" s="13"/>
+      <c r="C173" s="13"/>
+      <c r="D173" s="13"/>
       <c r="E173" s="7" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="13"/>
-      <c r="B174" s="12"/>
-      <c r="C174" s="12"/>
-      <c r="D174" s="12"/>
+      <c r="A174" s="12"/>
+      <c r="B174" s="13"/>
+      <c r="C174" s="13"/>
+      <c r="D174" s="13"/>
       <c r="E174" s="8"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="13"/>
-      <c r="B175" s="12"/>
-      <c r="C175" s="12"/>
-      <c r="D175" s="12"/>
+      <c r="A175" s="12"/>
+      <c r="B175" s="13"/>
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
       <c r="E175" s="7" t="s">
         <v>222</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="A2:A21"/>
-    <mergeCell ref="C2:C21"/>
-    <mergeCell ref="D2:D21"/>
-    <mergeCell ref="A22:A32"/>
-    <mergeCell ref="C22:C32"/>
-    <mergeCell ref="D22:D32"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="B22:B32"/>
-    <mergeCell ref="A33:A45"/>
-    <mergeCell ref="C33:C45"/>
-    <mergeCell ref="D33:D45"/>
-    <mergeCell ref="A46:A58"/>
-    <mergeCell ref="C46:C58"/>
-    <mergeCell ref="D46:D58"/>
-    <mergeCell ref="B33:B45"/>
-    <mergeCell ref="B46:B58"/>
-    <mergeCell ref="B70:B78"/>
-    <mergeCell ref="B79:B89"/>
-    <mergeCell ref="A59:A69"/>
-    <mergeCell ref="C59:C69"/>
-    <mergeCell ref="D59:D69"/>
-    <mergeCell ref="A70:A78"/>
-    <mergeCell ref="C70:C78"/>
-    <mergeCell ref="D70:D78"/>
-    <mergeCell ref="B59:B69"/>
-    <mergeCell ref="B90:B98"/>
-    <mergeCell ref="B99:B111"/>
-    <mergeCell ref="A79:A89"/>
-    <mergeCell ref="C79:C89"/>
-    <mergeCell ref="D79:D89"/>
-    <mergeCell ref="A90:A98"/>
-    <mergeCell ref="C90:C98"/>
-    <mergeCell ref="D90:D98"/>
-    <mergeCell ref="B112:B122"/>
-    <mergeCell ref="B123:B133"/>
-    <mergeCell ref="A99:A111"/>
-    <mergeCell ref="C99:C111"/>
-    <mergeCell ref="D99:D111"/>
-    <mergeCell ref="A112:A122"/>
-    <mergeCell ref="C112:C122"/>
-    <mergeCell ref="D112:D122"/>
-    <mergeCell ref="B134:B144"/>
-    <mergeCell ref="A123:A133"/>
-    <mergeCell ref="C123:C133"/>
-    <mergeCell ref="D123:D133"/>
-    <mergeCell ref="A134:A144"/>
-    <mergeCell ref="C134:C144"/>
-    <mergeCell ref="D134:D144"/>
     <mergeCell ref="D167:D175"/>
     <mergeCell ref="A145:A155"/>
     <mergeCell ref="C145:C155"/>
@@ -4714,6 +4668,54 @@
     <mergeCell ref="B167:B175"/>
     <mergeCell ref="A167:A175"/>
     <mergeCell ref="C167:C175"/>
+    <mergeCell ref="B134:B144"/>
+    <mergeCell ref="A123:A133"/>
+    <mergeCell ref="C123:C133"/>
+    <mergeCell ref="D123:D133"/>
+    <mergeCell ref="A134:A144"/>
+    <mergeCell ref="C134:C144"/>
+    <mergeCell ref="D134:D144"/>
+    <mergeCell ref="B112:B122"/>
+    <mergeCell ref="B123:B133"/>
+    <mergeCell ref="A99:A111"/>
+    <mergeCell ref="C99:C111"/>
+    <mergeCell ref="D99:D111"/>
+    <mergeCell ref="A112:A122"/>
+    <mergeCell ref="C112:C122"/>
+    <mergeCell ref="D112:D122"/>
+    <mergeCell ref="B90:B98"/>
+    <mergeCell ref="B99:B111"/>
+    <mergeCell ref="A79:A89"/>
+    <mergeCell ref="C79:C89"/>
+    <mergeCell ref="D79:D89"/>
+    <mergeCell ref="A90:A98"/>
+    <mergeCell ref="C90:C98"/>
+    <mergeCell ref="D90:D98"/>
+    <mergeCell ref="B70:B78"/>
+    <mergeCell ref="B79:B89"/>
+    <mergeCell ref="A59:A69"/>
+    <mergeCell ref="C59:C69"/>
+    <mergeCell ref="D59:D69"/>
+    <mergeCell ref="A70:A78"/>
+    <mergeCell ref="C70:C78"/>
+    <mergeCell ref="D70:D78"/>
+    <mergeCell ref="B59:B69"/>
+    <mergeCell ref="A33:A45"/>
+    <mergeCell ref="C33:C45"/>
+    <mergeCell ref="D33:D45"/>
+    <mergeCell ref="A46:A58"/>
+    <mergeCell ref="C46:C58"/>
+    <mergeCell ref="D46:D58"/>
+    <mergeCell ref="B33:B45"/>
+    <mergeCell ref="B46:B58"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="C2:C21"/>
+    <mergeCell ref="D2:D21"/>
+    <mergeCell ref="A22:A32"/>
+    <mergeCell ref="C22:C32"/>
+    <mergeCell ref="D22:D32"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="B22:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
